--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492698</v>
       </c>
       <c r="B2" t="n">
-        <v>57504</v>
+        <v>57507</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492698</v>
       </c>
       <c r="B2" t="n">
-        <v>57507</v>
+        <v>57508</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492698</v>
       </c>
       <c r="B2" t="n">
-        <v>57508</v>
+        <v>57509</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>121492698</v>
       </c>
       <c r="B2" t="n">
-        <v>57509</v>
+        <v>57510</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -778,6 +778,125 @@
           <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
         </is>
       </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126196688</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57812</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Bodviktorpet, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>612364</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7122701</v>
+      </c>
+      <c r="S3" t="n">
+        <v>37</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-06-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:50</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Niklas Holmström</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126196688</v>
       </c>
       <c r="B3" t="n">
-        <v>57812</v>
+        <v>57816</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -784,7 +784,7 @@
         <v>126196688</v>
       </c>
       <c r="B3" t="n">
-        <v>57816</v>
+        <v>57817</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -897,6 +897,240 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134300629</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58410</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>103001</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Rödvingetrast</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Turdus iliacus</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Forsvik, Forsvik, Åsele k:n, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>612242</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7122866</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Elias Ernvik</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Elias Ernvik</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134300642</v>
+      </c>
+      <c r="B5" t="n">
+        <v>58658</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103044</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Grönsiska</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Spinus spinus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Forsvik, Forsvik, Åsele k:n, Ås lm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>612242</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7122866</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Åsele lappmark</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>09:07</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Elias Ernvik</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Elias Ernvik</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121492698</v>
+        <v>134300629</v>
       </c>
       <c r="B2" t="n">
-        <v>57510</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,37 +686,49 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103021</v>
+        <v>103001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rödvingetrast</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Turdus iliacus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>Linnaeus, 1766</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stenkullafors-Åsele, Ås lm</t>
+          <t>Forsvik, Forsvik, Åsele k:n, Ås lm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>612458</v>
+        <v>612242</v>
       </c>
       <c r="R2" t="n">
-        <v>7122643</v>
+        <v>7122866</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,12 +752,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2024-10-01</t>
+          <t>2026-06-11</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>09:07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -765,26 +782,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Samuel Holdar</t>
+          <t>Elias Ernvik</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Samuel Holdar, Annika Rastén</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
-        </is>
-      </c>
+          <t>Elias Ernvik</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>126196688</v>
+        <v>121492698</v>
       </c>
       <c r="B3" t="n">
-        <v>57817</v>
+        <v>58114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,32 +822,20 @@
           <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Bodviktorpet, Ås lm</t>
+          <t>Stenkullafors-Åsele, Ås lm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>612364</v>
+        <v>612458</v>
       </c>
       <c r="R3" t="n">
-        <v>7122701</v>
+        <v>7122643</v>
       </c>
       <c r="S3" t="n">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,22 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-25</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>09:50</t>
+          <t>2024-10-01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,22 +879,26 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
+          <t>Samuel Holdar</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Niklas Holmström</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr"/>
+          <t>Samuel Holdar, Annika Rastén</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134300629</v>
+        <v>126196688</v>
       </c>
       <c r="B4" t="n">
-        <v>58410</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -911,49 +906,49 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103001</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rödvingetrast</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Turdus iliacus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1766</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Forsvik, Forsvik, Åsele k:n, Ås lm</t>
+          <t>Bodviktorpet, Ås lm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>612242</v>
+        <v>612364</v>
       </c>
       <c r="R4" t="n">
-        <v>7122866</v>
+        <v>7122701</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>37</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,22 +972,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2026-06-11</t>
+          <t>2025-06-25</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>09:07</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1007,12 +1002,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Elias Ernvik</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Elias Ernvik</t>
+          <t>Niklas Holmström</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>

--- a/artfynd/A 26897-2023 artfynd.xlsx
+++ b/artfynd/A 26897-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AZ5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134300629</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,6 +902,11 @@
           <t>EEN0087 Stenkullafors-Åsele NVI 2024</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121492698</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1011,6 +1026,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126196688</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1126,8 +1146,19 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134300642</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>